--- a/Nele/höhenprofile/Meu-nass/MN.xlsx
+++ b/Nele/höhenprofile/Meu-nass/MN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nele\OneDrive - Technische Universität Ilmenau\Dokumente\Moore-Lichtenau-Meusebach\Nele\höhenprofile\Meu-nass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AABB90D-7A38-4BA5-AF63-AF953A8F9CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B610C2F9-400E-42C5-BD6D-836025C4753C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{30A6721F-CEEA-447D-BB7A-51CAAC8EAE52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{30A6721F-CEEA-447D-BB7A-51CAAC8EAE52}"/>
   </bookViews>
   <sheets>
     <sheet name="WM" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="3">
   <si>
     <t>X</t>
   </si>
@@ -132,6 +132,1203 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Meusebach</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> nass - West -&gt; Mitte</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>WM!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>WM!$C$2:$C$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="47"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.50000000000000122</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5000000000000062</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0000000000000058</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5000000000000058</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0000000000000062</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5000000000000062</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.0000000000000124</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5000000000000124</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.0000000000000115</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.4999999999999698</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.4999999999999698</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.4999999999999698</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.4999999999999698</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10.49999999999997</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11.49999999999997</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.50000000000003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.500000000000032</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>14.500000000000032</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.500000000000032</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>16.500000000000032</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17.500000000000028</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18.500000000000028</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.500000000000028</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>20.500000000000032</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>21.500000000000028</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>22.500000000000032</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>22.500000000000032</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>WM!$D$2:$D$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="47"/>
+                <c:pt idx="0">
+                  <c:v>367.34504714791302</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>367.365167539472</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>367.44900018491501</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>367.57426897884199</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>367.65297857227802</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>367.59084231114298</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>367.425416714932</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>367.33293460494201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>367.24467335020199</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>367.114297787037</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>366.977216043932</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>366.96123373227402</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>366.91863204048099</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>366.83860456540202</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>366.80387315889999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>366.80447679180003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>366.78077792727902</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>366.77611049922001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>366.79561971543302</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>366.81308326904599</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>366.863675552578</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>366.91980313609702</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>366.85479063801301</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>366.79142381154998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>366.78540446099402</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>366.789605309823</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>366.79529052271198</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>366.80550959616102</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>366.80187157261798</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>366.79677234183401</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>366.89395808334598</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>366.894587376218</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>366.854513831068</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>366.86488493960701</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>366.895930944508</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>366.90525919464199</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>366.90486936349498</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>366.91802417369303</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>366.90475590870199</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>366.87358335950199</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>366.89096491747802</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>366.932431116923</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>366.97105374632599</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>366.98594765255802</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>366.94576762120602</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>366.97721384368901</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>366.97721384368901</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6DC6-4B20-8243-3DFBCFCF1769}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="520963960"/>
+        <c:axId val="520967560"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="520963960"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="520967560"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="520967560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="520963960"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>561976</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>61914</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A82B0F50-D92A-EF3B-0975-9864AA49739A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,13 +1644,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8227544C-2F47-40CE-9ED3-34FA2B96BAF3}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,8 +1661,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -475,8 +1676,11 @@
         <f>A2/$A$4</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>367.34504714791302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.818259827901752</v>
       </c>
@@ -487,8 +1691,11 @@
         <f t="shared" ref="C3:C48" si="0">A3/$A$4</f>
         <v>0.50000000000000122</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>367.365167539472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1.6365196558035</v>
       </c>
@@ -499,8 +1706,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>367.44900018491501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2.4547794837052499</v>
       </c>
@@ -511,8 +1721,11 @@
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>367.57426897884199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3.273039311607</v>
       </c>
@@ -523,8 +1736,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>367.65297857227802</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4.0912991395087603</v>
       </c>
@@ -535,8 +1751,11 @@
         <f t="shared" si="0"/>
         <v>2.5000000000000062</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>367.59084231114298</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4.9095589674105096</v>
       </c>
@@ -547,8 +1766,11 @@
         <f t="shared" si="0"/>
         <v>3.0000000000000058</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>367.425416714932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5.7278187953122597</v>
       </c>
@@ -559,8 +1781,11 @@
         <f t="shared" si="0"/>
         <v>3.5000000000000058</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>367.33293460494201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6.5460786232140098</v>
       </c>
@@ -571,8 +1796,11 @@
         <f t="shared" si="0"/>
         <v>4.0000000000000062</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>367.24467335020199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7.3643384511157599</v>
       </c>
@@ -583,8 +1811,11 @@
         <f t="shared" si="0"/>
         <v>4.5000000000000062</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>367.114297787037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8.1825982790175207</v>
       </c>
@@ -595,8 +1826,11 @@
         <f t="shared" si="0"/>
         <v>5.0000000000000124</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>366.977216043932</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9.0008581069192708</v>
       </c>
@@ -607,8 +1841,11 @@
         <f t="shared" si="0"/>
         <v>5.5000000000000124</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>366.96123373227402</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9.8191179348210191</v>
       </c>
@@ -619,8 +1856,11 @@
         <f t="shared" si="0"/>
         <v>6.0000000000000115</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>366.91863204048099</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>10.6373777627227</v>
       </c>
@@ -631,8 +1871,11 @@
         <f t="shared" si="0"/>
         <v>6.4999999999999698</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>366.83860456540202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>11.4556375906245</v>
       </c>
@@ -643,8 +1886,11 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>366.80387315889999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>12.2738974185262</v>
       </c>
@@ -655,8 +1901,11 @@
         <f t="shared" si="0"/>
         <v>7.4999999999999698</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>366.80447679180003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>13.092157246428</v>
       </c>
@@ -667,8 +1916,11 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>366.78077792727902</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>13.9104170743297</v>
       </c>
@@ -679,8 +1931,11 @@
         <f t="shared" si="0"/>
         <v>8.4999999999999698</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>366.77611049922001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>14.7286769022315</v>
       </c>
@@ -691,8 +1946,11 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>366.79561971543302</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>15.546936730133201</v>
       </c>
@@ -703,8 +1961,11 @@
         <f t="shared" si="0"/>
         <v>9.4999999999999698</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>366.81308326904599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>16.365196558034999</v>
       </c>
@@ -715,8 +1976,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>366.863675552578</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>17.183456385936701</v>
       </c>
@@ -727,8 +1991,11 @@
         <f t="shared" si="0"/>
         <v>10.49999999999997</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>366.91980313609702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>18.001716213838499</v>
       </c>
@@ -739,8 +2006,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>366.85479063801301</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>18.819976041740201</v>
       </c>
@@ -751,8 +2021,11 @@
         <f t="shared" si="0"/>
         <v>11.49999999999997</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>366.79142381154998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>19.638235869641999</v>
       </c>
@@ -763,8 +2036,11 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <v>366.78540446099402</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>20.456495697543801</v>
       </c>
@@ -775,8 +2051,11 @@
         <f t="shared" si="0"/>
         <v>12.50000000000003</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <v>366.789605309823</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>21.274755525445499</v>
       </c>
@@ -787,8 +2066,11 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>366.79529052271198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>22.093015353347301</v>
       </c>
@@ -799,8 +2081,11 @@
         <f t="shared" si="0"/>
         <v>13.500000000000032</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>366.80550959616102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>22.911275181249</v>
       </c>
@@ -811,8 +2096,11 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>366.80187157261798</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>23.729535009150801</v>
       </c>
@@ -823,8 +2111,11 @@
         <f t="shared" si="0"/>
         <v>14.500000000000032</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>366.79677234183401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>24.5477948370525</v>
       </c>
@@ -835,8 +2126,11 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>366.89395808334598</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>25.366054664954302</v>
       </c>
@@ -847,8 +2141,11 @@
         <f t="shared" si="0"/>
         <v>15.500000000000032</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>366.894587376218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26.184314492856</v>
       </c>
@@ -859,8 +2156,11 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>366.854513831068</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>27.002574320757802</v>
       </c>
@@ -871,8 +2171,11 @@
         <f t="shared" si="0"/>
         <v>16.500000000000032</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>366.86488493960701</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>27.8208341486595</v>
       </c>
@@ -883,8 +2186,11 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>366.895930944508</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>28.639093976561298</v>
       </c>
@@ -895,8 +2201,11 @@
         <f t="shared" si="0"/>
         <v>17.500000000000028</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>366.90525919464199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>29.457353804463001</v>
       </c>
@@ -907,8 +2216,11 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>366.90486936349498</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>30.275613632364799</v>
       </c>
@@ -919,8 +2231,11 @@
         <f t="shared" si="0"/>
         <v>18.500000000000028</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>366.91802417369303</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>31.093873460266501</v>
       </c>
@@ -931,8 +2246,11 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>366.90475590870199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>31.912133288168299</v>
       </c>
@@ -943,8 +2261,11 @@
         <f t="shared" si="0"/>
         <v>19.500000000000028</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>366.87358335950199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>32.730393116069997</v>
       </c>
@@ -955,8 +2276,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>366.89096491747802</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>33.548652943971803</v>
       </c>
@@ -967,8 +2291,11 @@
         <f t="shared" si="0"/>
         <v>20.500000000000032</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>366.932431116923</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>34.366912771873501</v>
       </c>
@@ -979,8 +2306,11 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>366.97105374632599</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>35.185172599775299</v>
       </c>
@@ -991,8 +2321,11 @@
         <f t="shared" si="0"/>
         <v>21.500000000000028</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>366.98594765255802</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>36.003432427676998</v>
       </c>
@@ -1003,8 +2336,11 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>366.94576762120602</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>36.821692255578803</v>
       </c>
@@ -1015,8 +2351,11 @@
         <f t="shared" si="0"/>
         <v>22.500000000000032</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <v>366.97721384368901</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>36.821692255578803</v>
       </c>
@@ -1027,9 +2366,13 @@
         <f t="shared" si="0"/>
         <v>22.500000000000032</v>
       </c>
+      <c r="D48">
+        <v>366.97721384368901</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
